--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.131.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.131.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.131.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.131.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.131.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.131.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0131.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0131.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -595,36 +595,40 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” This fo</t>
+          <t>L104: suspicious token(s): NoTE (odd internal casing) :: NoTE.— This fo</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: æ·±</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Creditorâ€™s Bill Blj a creditor upon the estate of a deceased person, seek-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]124</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]124</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: æ·±</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: -</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]124</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L36: punctuation artifact: double/multiple hyphen :: A. B., in the sum of Â£-----------------------, for goods sold and de-</t>
+          <t>L36: punctuation artifact: double/multiple hyphen :: A. B., in the sum of £-----------------------, for goods sold and de-</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,24 +672,24 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpa Ã¦ na, fc.)</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+6DF1 CJK UNIFIED IDEOGRAPH-6DF1 | isolated marker/symbol line :: 深</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This form may be varied according to the circumstances</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Order. The•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 124</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+6DF1 CJK UNIFIED IDEOGRAPH-6DF1 | isolated marker/symbol line :: 深</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L7: isolated marker/symbol line :: 0</t>
+          <t>L5: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -700,7 +704,7 @@
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>L52: abbreviation/spacing may be garbled :: A.B.,in the sum of Â£ Â£</t>
+          <t>L52: abbreviation/spacing may be garbled :: A.B.,in the sum of £ £</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr"/>
@@ -731,24 +735,24 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NorE.â€” This form may be varied according to the circumstances</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ， a</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: acter in which he claims is to be stated, as, â€œ to which debt the</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: named, is the €</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L33: symbol-only separator/garbage line :: . 1.</t>
+          <t>L32: isolated marker/symbol line :: 124</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: &amp;c.</t>
+          <t>L7: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -783,7 +787,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -792,24 +796,20 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” This fo</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: or assignee (mediate or immediate) of the said,â€� &amp;c.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr"/>
+          <t>L33: symbol-only separator/garbage line :: . 1.</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L100: isolated marker/symbol line :: &amp;c.</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
@@ -852,16 +852,12 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Order. Theâ€¢</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: f</t>
+          <t>L43: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -907,16 +903,12 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: named, is the â‚¬</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: , d</t>
+          <t>L44: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -958,16 +950,12 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This f</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: f.</t>
+          <t>L65: isolated marker/symbol line :: , d</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -1012,7 +1000,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ， a</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -1033,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1051,7 +1043,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L85: isolated marker/symbol line :: f.</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1077,7 +1073,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1111,12 +1107,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
